--- a/data/trending_integrated_20261030_09.xlsx
+++ b/data/trending_integrated_20261030_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1432000</v>
+        <v>20150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'-6.16%</t>
+          <t>'+123.89%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>800</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>493</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>1569</v>
+        <v>75</v>
       </c>
       <c r="H2" t="n">
-        <v>48.72</v>
+        <v>1.98</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1526000</v>
+        <v>9000</v>
       </c>
       <c r="K2" t="n">
-        <v>1444000</v>
+        <v>19290</v>
       </c>
       <c r="L2" t="n">
-        <v>1446000</v>
+        <v>21700</v>
       </c>
       <c r="M2" t="n">
-        <v>1427000</v>
+        <v>17920</v>
       </c>
       <c r="N2" t="n">
-        <v>48.66</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>276646525500</v>
+        <v>106511856440</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>21700</v>
       </c>
       <c r="Q2" t="n">
-        <v>501000</v>
+        <v>17920</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>시장 하락 및 주요 기업 실적 부진 속 SK하이닉스 주가 하락 전망. 3분기 실적 우려 및 외인 매도 가능성 언급.</t>
+          <t>단기 급등 및 변동성 높은 신규주 특성으로 인한 투자 주의 요구.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,20 +635,1032 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['3분기 실적', '외인 매도', '반도체']</t>
+          <t>['신규주', '단타', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>420610</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>서울반도체</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12790</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'+14.20%</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E3" t="n">
+        <v>154</v>
+      </c>
+      <c r="F3" t="n">
+        <v>108</v>
+      </c>
+      <c r="G3" t="n">
+        <v>479</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>11200</v>
+      </c>
+      <c r="K3" t="n">
+        <v>13500</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13710</v>
+      </c>
+      <c r="M3" t="n">
+        <v>12500</v>
+      </c>
+      <c r="N3" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="O3" t="n">
+        <v>12384558170</v>
+      </c>
+      <c r="P3" t="n">
+        <v>18960</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5730</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>희토류 없는 백색 LED 세계 최초 개발 발표. 100억 달러 시장 석권 기대.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['백색LED', '희토류', '시장 석권']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>046890</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>한화비전</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>49750</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'+1.32%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="E4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G4" t="n">
+        <v>92</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>49100</v>
+      </c>
+      <c r="K4" t="n">
+        <v>49450</v>
+      </c>
+      <c r="L4" t="n">
+        <v>50500</v>
+      </c>
+      <c r="M4" t="n">
+        <v>48050</v>
+      </c>
+      <c r="N4" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="O4" t="n">
+        <v>10586130550</v>
+      </c>
+      <c r="P4" t="n">
+        <v>97900</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>30950</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>사상 최대 실적 발표와 HBM, 보안 관련 모멘텀으로 인한 주가 상승 기대.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['실적', 'HBM', '보안']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>489790</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>15440</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'-1.78%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>124</v>
+      </c>
+      <c r="H5" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>15720</v>
+      </c>
+      <c r="K5" t="n">
+        <v>15420</v>
+      </c>
+      <c r="L5" t="n">
+        <v>15700</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15320</v>
+      </c>
+      <c r="N5" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5763887280</v>
+      </c>
+      <c r="P5" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>15320</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>미국 조선주 강세 속에서 신용 물량 출회 및 주가 하락 우려.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['조선', '신용', '외국인']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>223500</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-3.66%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E6" t="n">
+        <v>800</v>
+      </c>
+      <c r="F6" t="n">
+        <v>541</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1493</v>
+      </c>
+      <c r="H6" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>232000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>223500</v>
+      </c>
+      <c r="L6" t="n">
+        <v>229500</v>
+      </c>
+      <c r="M6" t="n">
+        <v>222000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="O6" t="n">
+        <v>626306885750</v>
+      </c>
+      <c r="P6" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>94500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>정치적 논란과 주주 가치 훼손 논란 속에서 배당 관련 긍정적 기대감도 혼재.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['정치', '배당', '상속세']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
         <v>21</v>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>54200</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-4.41%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>126</v>
+      </c>
+      <c r="F7" t="n">
+        <v>90</v>
+      </c>
+      <c r="G7" t="n">
+        <v>512</v>
+      </c>
+      <c r="H7" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>56700</v>
+      </c>
+      <c r="K7" t="n">
+        <v>55500</v>
+      </c>
+      <c r="L7" t="n">
+        <v>55900</v>
+      </c>
+      <c r="M7" t="n">
+        <v>54000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="O7" t="n">
+        <v>17399563350</v>
+      </c>
+      <c r="P7" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>53400</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>미국 SMR 원자로 수주 및 실적 개선 소식에 따른 긍정적 전망.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['SMR', '원전', '수주']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11030</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-5.08%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>153</v>
+      </c>
+      <c r="F8" t="n">
+        <v>97</v>
+      </c>
+      <c r="G8" t="n">
+        <v>525</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>11620</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11300</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11470</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10960</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>13192129995</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>원전 사업 불확실성과 공매도 금지 조치 속에서 재건 사업 기대감 존재.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['원전', '공매도', '재건']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14170</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-5.72%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>42</v>
+      </c>
+      <c r="F9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" t="n">
+        <v>151</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>15030</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14570</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14010</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="O9" t="n">
+        <v>11621494530</v>
+      </c>
+      <c r="P9" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1830</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>전반적인 시장 하락 속 광통신 섹터 조정 예상.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['광통신', '조정', '시장 하락']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1418000</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-7.08%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>800</v>
+      </c>
+      <c r="F10" t="n">
+        <v>497</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="H10" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1526000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1444000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1446000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1408000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="O10" t="n">
+        <v>720810100500</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>501000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>반도체 업황 둔화 우려 및 외인 매도세 속 주가 하락세 지속.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['반도체', '외인', '실적']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>한화솔루션</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>21450</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-9.11%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="E11" t="n">
+        <v>78</v>
+      </c>
+      <c r="F11" t="n">
+        <v>72</v>
+      </c>
+      <c r="G11" t="n">
+        <v>214</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>23600</v>
+      </c>
+      <c r="K11" t="n">
+        <v>22650</v>
+      </c>
+      <c r="L11" t="n">
+        <v>22700</v>
+      </c>
+      <c r="M11" t="n">
+        <v>21350</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="O11" t="n">
+        <v>23780014425</v>
+      </c>
+      <c r="P11" t="n">
+        <v>59300</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>21350</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>태양광 사업 호조에도 불구하고 주가 급락 및 의혹 제기로 투자 심리 위축.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['태양광', '주가조작', 'RE100']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>009830</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>멜콘</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13450</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-20.88%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" t="n">
+        <v>37</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>17000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14900</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13260</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O12" t="n">
+        <v>14344233470</v>
+      </c>
+      <c r="P12" t="n">
+        <v>28800</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>11550</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>반도체 업황 부진 및 보호예수 해제 물량 부담으로 인한 주가 급락.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['반도체', '보호예수', '급락']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10730</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-28.47%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>47</v>
+      </c>
+      <c r="F13" t="n">
+        <v>36</v>
+      </c>
+      <c r="G13" t="n">
+        <v>21</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12700</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9800</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>34601668855</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12700</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>9800</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>상장 첫날 급락하며 공모주 시장 부진 및 높은 변동성 시현.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['공모주', '하한가', '변동성']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>439270</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261030_09.xlsx
+++ b/data/trending_integrated_20261030_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20150</v>
+        <v>19850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+123.89%</t>
+          <t>'+120.56%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>106511856440</v>
+        <v>124934566005</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>단기 급등 및 변동성 높은 신규주 특성으로 인한 투자 주의 요구.</t>
+          <t>신규 상장 후 단기 급등세. 높은 상승률과 유통 물량 제한 속에 추가 상승 기대감 형성. 다만, 높은 변동성에 대한 주의도 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규주', '단타', '변동성']</t>
+          <t>['신규주', '단타', '유통 물량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12790</v>
+        <v>12750</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.20%</t>
+          <t>'+13.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G3" t="n">
-        <v>479</v>
+        <v>502</v>
       </c>
       <c r="H3" t="n">
         <v>15.04</v>
@@ -702,7 +702,7 @@
         <v>15.08</v>
       </c>
       <c r="O3" t="n">
-        <v>12384558170</v>
+        <v>16085617455</v>
       </c>
       <c r="P3" t="n">
         <v>18960</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49750</v>
+        <v>51000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.32%</t>
+          <t>'+3.87%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.82</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
         <v>23.82</v>
@@ -785,7 +785,7 @@
         <v>49450</v>
       </c>
       <c r="L4" t="n">
-        <v>50500</v>
+        <v>51400</v>
       </c>
       <c r="M4" t="n">
         <v>48050</v>
@@ -794,7 +794,7 @@
         <v>24.64</v>
       </c>
       <c r="O4" t="n">
-        <v>10586130550</v>
+        <v>18920200600</v>
       </c>
       <c r="P4" t="n">
         <v>97900</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표와 HBM, 보안 관련 모멘텀으로 인한 주가 상승 기대.</t>
+          <t>사상 최대 실적 발표에도 불구하고 주가 하락. 공매도 기관과의 공방 속 과매도 구간 진입 후 반등 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['실적', 'HBM', '보안']</t>
+          <t>['실적', '공매도', '과매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15440</v>
+        <v>15710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.78%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="H5" t="n">
         <v>28.13</v>
@@ -877,7 +877,7 @@
         <v>15420</v>
       </c>
       <c r="L5" t="n">
-        <v>15700</v>
+        <v>15720</v>
       </c>
       <c r="M5" t="n">
         <v>15320</v>
@@ -886,7 +886,7 @@
         <v>28.07</v>
       </c>
       <c r="O5" t="n">
-        <v>5763887280</v>
+        <v>8916014535</v>
       </c>
       <c r="P5" t="n">
         <v>35350</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 조선주 강세 속에서 신용 물량 출회 및 주가 하락 우려.</t>
+          <t>미국 조선주 급등과 대비되는 한국 조선주 부진. 신용 물량 및 연기금 매도세 출현으로 인한 주가 하락 우려. 11월 1만원 이하 추락 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['조선', '신용', '외국인']</t>
+          <t>['조선주', '신용 물량', '연기금']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>223500</v>
+        <v>54700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>142</v>
       </c>
       <c r="F6" t="n">
-        <v>541</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>1493</v>
+        <v>553</v>
       </c>
       <c r="H6" t="n">
-        <v>46.17</v>
+        <v>22.14</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>232000</v>
+        <v>56700</v>
       </c>
       <c r="K6" t="n">
-        <v>223500</v>
+        <v>55500</v>
       </c>
       <c r="L6" t="n">
-        <v>229500</v>
+        <v>55900</v>
       </c>
       <c r="M6" t="n">
-        <v>222000</v>
+        <v>54000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.19</v>
+        <v>22.34</v>
       </c>
       <c r="O6" t="n">
-        <v>626306885750</v>
+        <v>22133635550</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>53400</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -994,20 +994,20 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 논란과 주주 가치 훼손 논란 속에서 배당 관련 긍정적 기대감도 혼재.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 소식. 체코 원전 수주 실패에도 불구하고 미 증시 원전주 대체 효과 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['정치', '배당', '상속세']</t>
+          <t>['SMR', '뉴스케일파워', '원전']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54200</v>
+        <v>11200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.2</v>
+        <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G7" t="n">
-        <v>512</v>
+        <v>577</v>
       </c>
       <c r="H7" t="n">
-        <v>22.14</v>
+        <v>9.73</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>56700</v>
+        <v>11620</v>
       </c>
       <c r="K7" t="n">
-        <v>55500</v>
+        <v>11300</v>
       </c>
       <c r="L7" t="n">
-        <v>55900</v>
+        <v>11470</v>
       </c>
       <c r="M7" t="n">
-        <v>54000</v>
+        <v>10960</v>
       </c>
       <c r="N7" t="n">
-        <v>22.34</v>
+        <v>9.6</v>
       </c>
       <c r="O7" t="n">
-        <v>17399563350</v>
+        <v>17418158220</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>53400</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1086,20 +1086,20 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 SMR 원자로 수주 및 실적 개선 소식에 따른 긍정적 전망.</t>
+          <t>원전 및 가덕도 공사비 증액 관련 논란 속 공매도 금지 조치. 러시아, 우크라이나, 중동 재건 사업 기대감 속 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['SMR', '원전', '수주']</t>
+          <t>['원전', '공매도 금지', '가덕도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11030</v>
+        <v>223250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-5.08%</t>
+          <t>'-3.77%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>97</v>
+        <v>531</v>
       </c>
       <c r="G8" t="n">
-        <v>525</v>
+        <v>1408</v>
       </c>
       <c r="H8" t="n">
-        <v>9.73</v>
+        <v>46.17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,28 +1147,28 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11620</v>
+        <v>232000</v>
       </c>
       <c r="K8" t="n">
-        <v>11300</v>
+        <v>223500</v>
       </c>
       <c r="L8" t="n">
-        <v>11470</v>
+        <v>229500</v>
       </c>
       <c r="M8" t="n">
-        <v>10960</v>
+        <v>222000</v>
       </c>
       <c r="N8" t="n">
-        <v>9.6</v>
+        <v>46.19</v>
       </c>
       <c r="O8" t="n">
-        <v>13192129995</v>
+        <v>774539280500</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원전 사업 불확실성과 공매도 금지 조치 속에서 재건 사업 기대감 존재.</t>
+          <t>이재명 대통령 및 이재용 회장에 대한 비판과 함께 삼성전자 주가 하락에 대한 불만을 표출. 대주주 상속세 절감을 위한 의도적 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '재건']</t>
+          <t>['상속세', '주가 조작', '레버리지']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14170</v>
+        <v>14230</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-5.72%</t>
+          <t>'-5.32%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.2</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="H9" t="n">
         <v>3.13</v>
@@ -1254,7 +1254,7 @@
         <v>3.33</v>
       </c>
       <c r="O9" t="n">
-        <v>11621494530</v>
+        <v>14395311340</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>전반적인 시장 하락 속 광통신 섹터 조정 예상.</t>
+          <t>광통신 테마의 전반적인 하락세 속에서 개별 종목의 급락 및 개인 투자자들의 혼조된 심리가 나타나고 있다. 목표가 제시 및 매수 기회 언급이 있으나, 주가 하락 우려와 부정적인 전망이 주를 이룬다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '조정', '시장 하락']</t>
+          <t>['광통신', '데드크로스', '주가 하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1418000</v>
+        <v>1425000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-7.08%</t>
+          <t>'-6.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="G10" t="n">
-        <v>1481</v>
+        <v>1496</v>
       </c>
       <c r="H10" t="n">
         <v>48.72</v>
@@ -1346,7 +1346,7 @@
         <v>48.66</v>
       </c>
       <c r="O10" t="n">
-        <v>720810100500</v>
+        <v>916633749500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 업황 둔화 우려 및 외인 매도세 속 주가 하락세 지속.</t>
+          <t>미국 증시 및 구글 급락에 따른 SK하이닉스 주가 하락 우려. 외인 대량 매도 및 주가 방어 실패 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '외인', '실적']</t>
+          <t>['반도체', '외인 매도', '실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21450</v>
+        <v>22000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-9.11%</t>
+          <t>'-6.78%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.63</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G11" t="n">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="H11" t="n">
         <v>11.6</v>
@@ -1432,19 +1432,19 @@
         <v>22700</v>
       </c>
       <c r="M11" t="n">
-        <v>21350</v>
+        <v>21100</v>
       </c>
       <c r="N11" t="n">
         <v>12.23</v>
       </c>
       <c r="O11" t="n">
-        <v>23780014425</v>
+        <v>33667881525</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
       </c>
       <c r="Q11" t="n">
-        <v>21350</v>
+        <v>21100</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>태양광 사업 호조에도 불구하고 주가 급락 및 의혹 제기로 투자 심리 위축.</t>
+          <t>한화 김동원 부회장 주가 누르기 의혹 제기. 미국 카터스빌 모듈 물량 완판 및 RE100 승인 등 호재에도 불구하고 주가 급락.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['태양광', '주가조작', 'RE100']</t>
+          <t>['주가 누르기', '태양광', 'RE100']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13450</v>
+        <v>13600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-20.88%</t>
+          <t>'-20.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.01</v>
       </c>
       <c r="E12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G12" t="n">
         <v>44</v>
-      </c>
-      <c r="F12" t="n">
-        <v>30</v>
-      </c>
-      <c r="G12" t="n">
-        <v>37</v>
       </c>
       <c r="H12" t="n">
         <v>0.66</v>
@@ -1530,7 +1530,7 @@
         <v>0.65</v>
       </c>
       <c r="O12" t="n">
-        <v>14344233470</v>
+        <v>17860407605</v>
       </c>
       <c r="P12" t="n">
         <v>28800</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 및 보호예수 해제 물량 부담으로 인한 주가 급락.</t>
+          <t>반도체 업황 부진 및 신규 상장 종목의 급락세. HBM, 데이터센터 관련 호재에도 불구하고 보호예수 해제 및 매도 물량 출현으로 인한 주가 하락.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '보호예수', '급락']</t>
+          <t>['반도체', 'HBM', '보호예수']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10730</v>
+        <v>10640</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-28.47%</t>
+          <t>'-29.07%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="H13" t="n">
         <v>3.05</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>34601668855</v>
+        <v>39366846540</v>
       </c>
       <c r="P13" t="n">
         <v>12700</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>상장 첫날 급락하며 공모주 시장 부진 및 높은 변동성 시현.</t>
+          <t>공모주 시장 침체 속 신규 상장 종목의 하한가 예상. 높은 당기순이익과 구독 시스템에도 불구하고 밸류에이션 부재 및 기관 매도세 지적.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공모주', '하한가', '변동성']</t>
+          <t>['공모주', '하한가', '밸류에이션']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261030_09.xlsx
+++ b/data/trending_integrated_20261030_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19850</v>
+        <v>19990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+120.56%</t>
+          <t>'+122.11%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>124934566005</v>
+        <v>148396071465</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
@@ -619,23 +619,23 @@
         <v>17920</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장 후 단기 급등세. 높은 상승률과 유통 물량 제한 속에 추가 상승 기대감 형성. 다만, 높은 변동성에 대한 주의도 언급.</t>
+          <t>신규 상장 종목으로 단기 급등 가능성.  상장 첫날 높은 변동성 및 투자자들의 단기 차익 실현 욕구.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규주', '단타', '유통 물량']</t>
+          <t>['신규상장', '단타', '유통물량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12750</v>
+        <v>12530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.84%</t>
+          <t>'+11.88%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="F3" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G3" t="n">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="H3" t="n">
         <v>15.04</v>
@@ -696,13 +696,13 @@
         <v>13710</v>
       </c>
       <c r="M3" t="n">
-        <v>12500</v>
+        <v>12310</v>
       </c>
       <c r="N3" t="n">
         <v>15.08</v>
       </c>
       <c r="O3" t="n">
-        <v>16085617455</v>
+        <v>19132719445</v>
       </c>
       <c r="P3" t="n">
         <v>18960</v>
@@ -711,7 +711,7 @@
         <v>5730</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-191000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>상지건설</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51000</v>
+        <v>6770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.87%</t>
+          <t>'+8.49%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="H4" t="n">
-        <v>23.82</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>49100</v>
+        <v>6240</v>
       </c>
       <c r="K4" t="n">
-        <v>49450</v>
+        <v>6700</v>
       </c>
       <c r="L4" t="n">
-        <v>51400</v>
+        <v>7670</v>
       </c>
       <c r="M4" t="n">
-        <v>48050</v>
+        <v>6330</v>
       </c>
       <c r="N4" t="n">
-        <v>24.64</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>18920200600</v>
+        <v>10703498155</v>
       </c>
       <c r="P4" t="n">
-        <v>97900</v>
+        <v>16620</v>
       </c>
       <c r="Q4" t="n">
-        <v>30950</v>
+        <v>4600</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표에도 불구하고 주가 하락. 공매도 기관과의 공방 속 과매도 구간 진입 후 반등 기대.</t>
+          <t>건설 산업 회복 및 재건 사업 기대감.  주봉 분석 기반의 상승 가능성과 유상증자, 지수 폭락 등 투자 불확실성 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '과매도']</t>
+          <t>['건설', '재건', '유상증자']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>042940</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15710</v>
+        <v>51100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'+4.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.06</v>
+        <v>-0.82</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="H5" t="n">
-        <v>28.13</v>
+        <v>23.82</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>15720</v>
+        <v>49100</v>
       </c>
       <c r="K5" t="n">
-        <v>15420</v>
+        <v>49450</v>
       </c>
       <c r="L5" t="n">
-        <v>15720</v>
+        <v>52000</v>
       </c>
       <c r="M5" t="n">
-        <v>15320</v>
+        <v>48050</v>
       </c>
       <c r="N5" t="n">
-        <v>28.07</v>
+        <v>24.64</v>
       </c>
       <c r="O5" t="n">
-        <v>8916014535</v>
+        <v>24559979600</v>
       </c>
       <c r="P5" t="n">
-        <v>35350</v>
+        <v>97900</v>
       </c>
       <c r="Q5" t="n">
-        <v>15320</v>
+        <v>30950</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-86000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 조선주 급등과 대비되는 한국 조선주 부진. 신용 물량 및 연기금 매도세 출현으로 인한 주가 하락 우려. 11월 1만원 이하 추락 가능성 언급.</t>
+          <t>최대 실적 발표 및 TC본더 매출 본격화 등 긍정적 실적 기반.  미국 장세 영향 및 과매도 구간에서의 반등 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['조선주', '신용 물량', '연기금']</t>
+          <t>['실적', 'TC본더', '과매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54700</v>
+        <v>15930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'+1.34%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>553</v>
+        <v>155</v>
       </c>
       <c r="H6" t="n">
-        <v>22.14</v>
+        <v>28.13</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>56700</v>
+        <v>15720</v>
       </c>
       <c r="K6" t="n">
-        <v>55500</v>
+        <v>15420</v>
       </c>
       <c r="L6" t="n">
-        <v>55900</v>
+        <v>15960</v>
       </c>
       <c r="M6" t="n">
-        <v>54000</v>
+        <v>15320</v>
       </c>
       <c r="N6" t="n">
-        <v>22.34</v>
+        <v>28.07</v>
       </c>
       <c r="O6" t="n">
-        <v>22133635550</v>
+        <v>13522868740</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q6" t="n">
-        <v>53400</v>
+        <v>15320</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>143000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 소식. 체코 원전 수주 실패에도 불구하고 미 증시 원전주 대체 효과 기대.</t>
+          <t>미국 조선주 급등 속 국내 증시 부진.  신용 물량 출회 및 기관 매도 우려.  하반기 산타랠리 기대감과 종목 자체의 변동성에 대한 불안감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['SMR', '뉴스케일파워', '원전']</t>
+          <t>['조선주', '신용물량', '산타랠리']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11200</v>
+        <v>11340</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-2.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="F7" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G7" t="n">
-        <v>577</v>
+        <v>642</v>
       </c>
       <c r="H7" t="n">
         <v>9.73</v>
@@ -1070,7 +1070,7 @@
         <v>9.6</v>
       </c>
       <c r="O7" t="n">
-        <v>17418158220</v>
+        <v>20373415205</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1079,14 +1079,14 @@
         <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 및 가덕도 공사비 증액 관련 논란 속 공매도 금지 조치. 러시아, 우크라이나, 중동 재건 사업 기대감 속 주가 하락 우려.</t>
+          <t>공매도 금지 조치 및 원전, 가덕도 공사비 증액 등 정부 정책 관련 긍정적 기대감.  한수원과의 협상 및 재입찰 관련 불확실성 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '공매도 금지', '가덕도']</t>
+          <t>['공매도금지', '원전', '가덕도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>223250</v>
+        <v>55300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.77%</t>
+          <t>'-2.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>149</v>
       </c>
       <c r="F8" t="n">
-        <v>531</v>
+        <v>102</v>
       </c>
       <c r="G8" t="n">
-        <v>1408</v>
+        <v>580</v>
       </c>
       <c r="H8" t="n">
-        <v>46.17</v>
+        <v>22.14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>232000</v>
+        <v>56700</v>
       </c>
       <c r="K8" t="n">
-        <v>223500</v>
+        <v>55500</v>
       </c>
       <c r="L8" t="n">
-        <v>229500</v>
+        <v>55900</v>
       </c>
       <c r="M8" t="n">
-        <v>222000</v>
+        <v>54000</v>
       </c>
       <c r="N8" t="n">
-        <v>46.19</v>
+        <v>22.34</v>
       </c>
       <c r="O8" t="n">
-        <v>774539280500</v>
+        <v>26314008300</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>53400</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이재명 대통령 및 이재용 회장에 대한 비판과 함께 삼성전자 주가 하락에 대한 불만을 표출. 대주주 상속세 절감을 위한 의도적 주가 조작 의혹 제기.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 폴란드 원전 사업 기대감.  정부 정책 및 실적 부진에 대한 비판과 시장 변동성에 대한 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['상속세', '주가 조작', '레버리지']</t>
+          <t>['SMR', '원전', '뉴스케일']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14230</v>
+        <v>222500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-5.32%</t>
+          <t>'-4.09%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>539</v>
       </c>
       <c r="G9" t="n">
-        <v>164</v>
+        <v>1404</v>
       </c>
       <c r="H9" t="n">
-        <v>3.13</v>
+        <v>46.17</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>15030</v>
+        <v>232000</v>
       </c>
       <c r="K9" t="n">
-        <v>14500</v>
+        <v>223500</v>
       </c>
       <c r="L9" t="n">
-        <v>14570</v>
+        <v>229500</v>
       </c>
       <c r="M9" t="n">
-        <v>14010</v>
+        <v>221000</v>
       </c>
       <c r="N9" t="n">
-        <v>3.33</v>
+        <v>46.19</v>
       </c>
       <c r="O9" t="n">
-        <v>14395311340</v>
+        <v>918063697000</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>1830</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1198000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>광통신 테마의 전반적인 하락세 속에서 개별 종목의 급락 및 개인 투자자들의 혼조된 심리가 나타나고 있다. 목표가 제시 및 매수 기회 언급이 있으나, 주가 하락 우려와 부정적인 전망이 주를 이룬다.</t>
+          <t>이재용 증여세, 노조 주가 하락 기도 등 총수 관련 부정적 이슈와 해외 상장 기대감 혼재.  주가 변동성 및 국장 시장 전반에 대한 비판.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '데드크로스', '주가 하락']</t>
+          <t>['증여세', '노조', '레버리지']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1425000</v>
+        <v>14320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-6.62%</t>
+          <t>'-4.72%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.06</v>
+        <v>-0.2</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>506</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>1496</v>
+        <v>182</v>
       </c>
       <c r="H10" t="n">
-        <v>48.72</v>
+        <v>3.13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1526000</v>
+        <v>15030</v>
       </c>
       <c r="K10" t="n">
-        <v>1444000</v>
+        <v>14500</v>
       </c>
       <c r="L10" t="n">
-        <v>1446000</v>
+        <v>14570</v>
       </c>
       <c r="M10" t="n">
-        <v>1408000</v>
+        <v>14010</v>
       </c>
       <c r="N10" t="n">
-        <v>48.66</v>
+        <v>3.33</v>
       </c>
       <c r="O10" t="n">
-        <v>916633749500</v>
+        <v>17152014460</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>501000</v>
+        <v>1830</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 및 구글 급락에 따른 SK하이닉스 주가 하락 우려. 외인 대량 매도 및 주가 방어 실패 가능성 언급.</t>
+          <t>광통신 섹터 전반의 하락세와 개별 종목의 변동성에 대한 부정적 심리. 명확한 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '외인 매도', '실적']</t>
+          <t>['광통신', '변동성', '국장']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22000</v>
+        <v>1427000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.78%</t>
+          <t>'-6.49%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.63</v>
+        <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>85</v>
+        <v>504</v>
       </c>
       <c r="G11" t="n">
-        <v>251</v>
+        <v>1462</v>
       </c>
       <c r="H11" t="n">
-        <v>11.6</v>
+        <v>48.72</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>23600</v>
+        <v>1526000</v>
       </c>
       <c r="K11" t="n">
-        <v>22650</v>
+        <v>1444000</v>
       </c>
       <c r="L11" t="n">
-        <v>22700</v>
+        <v>1446000</v>
       </c>
       <c r="M11" t="n">
-        <v>21100</v>
+        <v>1408000</v>
       </c>
       <c r="N11" t="n">
-        <v>12.23</v>
+        <v>48.66</v>
       </c>
       <c r="O11" t="n">
-        <v>33667881525</v>
+        <v>1045317384000</v>
       </c>
       <c r="P11" t="n">
-        <v>59300</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>21100</v>
+        <v>501000</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>한화 김동원 부회장 주가 누르기 의혹 제기. 미국 카터스빌 모듈 물량 완판 및 RE100 승인 등 호재에도 불구하고 주가 급락.</t>
+          <t>반도체 업황 부진 및 외인 매도세 지속.  대규모 소각에도 주가 방어 실패, 하락 추세 강화.  향후 증시 및 개별 종목에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 누르기', '태양광', 'RE100']</t>
+          <t>['반도체', '외인매도', '소각']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13600</v>
+        <v>21900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-20.00%</t>
+          <t>'-7.20%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.63</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="G12" t="n">
-        <v>44</v>
+        <v>302</v>
       </c>
       <c r="H12" t="n">
-        <v>0.66</v>
+        <v>11.6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17000</v>
+        <v>23600</v>
       </c>
       <c r="K12" t="n">
-        <v>14000</v>
+        <v>22650</v>
       </c>
       <c r="L12" t="n">
-        <v>14900</v>
+        <v>22700</v>
       </c>
       <c r="M12" t="n">
-        <v>13260</v>
+        <v>21100</v>
       </c>
       <c r="N12" t="n">
-        <v>0.65</v>
+        <v>12.23</v>
       </c>
       <c r="O12" t="n">
-        <v>17860407605</v>
+        <v>39616600225</v>
       </c>
       <c r="P12" t="n">
-        <v>28800</v>
+        <v>59300</v>
       </c>
       <c r="Q12" t="n">
-        <v>11550</v>
+        <v>21100</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-368000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 및 신규 상장 종목의 급락세. HBM, 데이터센터 관련 호재에도 불구하고 보호예수 해제 및 매도 물량 출현으로 인한 주가 하락.</t>
+          <t>한화 김동원 부회장 주가 누르기 의혹 제기.  태양광 수혜 및 RE100 승인 호재와 급락세, IR 신뢰도 부족, 주가 조작 의혹 등 부정적 요인 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', 'HBM', '보호예수']</t>
+          <t>['태양광', 'RE100', '주가조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10640</v>
+        <v>13890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-29.07%</t>
+          <t>'-18.29%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H13" t="n">
-        <v>3.05</v>
+        <v>0.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,58 +1607,150 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="K13" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14900</v>
+      </c>
+      <c r="M13" t="n">
+        <v>13260</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O13" t="n">
+        <v>19428918305</v>
+      </c>
+      <c r="P13" t="n">
+        <v>28800</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>11550</v>
+      </c>
+      <c r="R13" t="n">
         <v>12000</v>
       </c>
-      <c r="L13" t="n">
-        <v>12700</v>
-      </c>
-      <c r="M13" t="n">
-        <v>9800</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>39366846540</v>
-      </c>
-      <c r="P13" t="n">
-        <v>12700</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>9800</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공모주 시장 침체 속 신규 상장 종목의 하한가 예상. 높은 당기순이익과 구독 시스템에도 불구하고 밸류에이션 부재 및 기관 매도세 지적.</t>
+          <t>반도체 업황 부진과 신규주 상장 관련 부정적 전망. 보호예수 해제 이후 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공모주', '하한가', '밸류에이션']</t>
+          <t>['반도체', '신규주', '보호예수']</t>
         </is>
       </c>
       <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10260</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-31.60%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>101</v>
+      </c>
+      <c r="F14" t="n">
+        <v>63</v>
+      </c>
+      <c r="G14" t="n">
+        <v>87</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>12700</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9800</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>43033260540</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12700</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9800</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-28000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>동시 상장 종목 대비 낮은 현재가와 높은 당기순이익.  공모주 시장 전반의 부진 및 투자자들의 부정적 심리.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['공모주', '당기순이익', '하한가']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
         <v>1</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>439270</t>
         </is>

--- a/data/trending_integrated_20261030_09.xlsx
+++ b/data/trending_integrated_20261030_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19990</v>
+        <v>19570</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+122.11%</t>
+          <t>'+117.44%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G2" t="n">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>148396071465</v>
+        <v>165991256720</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장 종목으로 단기 급등 가능성.  상장 첫날 높은 변동성 및 투자자들의 단기 차익 실현 욕구.</t>
+          <t>신규 상장 후 단기 급등세를 보이며 높은 수익률 기록. 유통 물량 적고 변동성 큰 특성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규상장', '단타', '유통물량']</t>
+          <t>['신규 상장', '단타', '유통 물량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12530</v>
+        <v>12600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.88%</t>
+          <t>'+12.50%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F3" t="n">
         <v>122</v>
       </c>
       <c r="G3" t="n">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="H3" t="n">
         <v>15.04</v>
@@ -696,13 +696,13 @@
         <v>13710</v>
       </c>
       <c r="M3" t="n">
-        <v>12310</v>
+        <v>12100</v>
       </c>
       <c r="N3" t="n">
         <v>15.08</v>
       </c>
       <c r="O3" t="n">
-        <v>19132719445</v>
+        <v>22165343120</v>
       </c>
       <c r="P3" t="n">
         <v>18960</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>희토류 없는 백색 LED 세계 최초 개발 발표. 100억 달러 시장 석권 기대.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 및 100억 달러 시장 석권 전망. 공매도 세력의 움직임과 높은 거래대금 기록.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6770</v>
+        <v>6680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.49%</t>
+          <t>'+7.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F4" t="n">
         <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>10703498155</v>
+        <v>11046430195</v>
       </c>
       <c r="P4" t="n">
         <v>16620</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>건설 산업 회복 및 재건 사업 기대감.  주봉 분석 기반의 상승 가능성과 유상증자, 지수 폭락 등 투자 불확실성 혼재.</t>
+          <t>건설 경기 전환점 및 풍부한 재료를 기반으로 한 주봉 차트 분석. 유상증자 이후의 불확실성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['건설', '재건', '유상증자']</t>
+          <t>['건설 경기', '주봉 차트', '유상증자']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51100</v>
+        <v>8900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.07%</t>
+          <t>'+3.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.82</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="H5" t="n">
-        <v>23.82</v>
+        <v>2.67</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>49100</v>
+        <v>8580</v>
       </c>
       <c r="K5" t="n">
-        <v>49450</v>
+        <v>11090</v>
       </c>
       <c r="L5" t="n">
-        <v>52000</v>
+        <v>11150</v>
       </c>
       <c r="M5" t="n">
-        <v>48050</v>
+        <v>8400</v>
       </c>
       <c r="N5" t="n">
-        <v>24.64</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>24559979600</v>
+        <v>17140192560</v>
       </c>
       <c r="P5" t="n">
-        <v>97900</v>
+        <v>19270</v>
       </c>
       <c r="Q5" t="n">
-        <v>30950</v>
+        <v>2135</v>
       </c>
       <c r="R5" t="n">
-        <v>-86000</v>
+        <v>-149000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>최대 실적 발표 및 TC본더 매출 본격화 등 긍정적 실적 기반.  미국 장세 영향 및 과매도 구간에서의 반등 가능성 언급.</t>
+          <t>인텔 어닝 쇼크 및 환기 관련 이슈로 인한 주가 변동성. 광통신 사업 및 혁신 기술 관련 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', '과매도']</t>
+          <t>['광통신', '환기', '혁신']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15930</v>
+        <v>50400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.34%</t>
+          <t>'+2.65%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.06</v>
+        <v>-0.82</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="H6" t="n">
-        <v>28.13</v>
+        <v>23.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>15720</v>
+        <v>49100</v>
       </c>
       <c r="K6" t="n">
-        <v>15420</v>
+        <v>49450</v>
       </c>
       <c r="L6" t="n">
-        <v>15960</v>
+        <v>52000</v>
       </c>
       <c r="M6" t="n">
-        <v>15320</v>
+        <v>48050</v>
       </c>
       <c r="N6" t="n">
-        <v>28.07</v>
+        <v>24.64</v>
       </c>
       <c r="O6" t="n">
-        <v>13522868740</v>
+        <v>29769251700</v>
       </c>
       <c r="P6" t="n">
-        <v>35350</v>
+        <v>97900</v>
       </c>
       <c r="Q6" t="n">
-        <v>15320</v>
+        <v>30950</v>
       </c>
       <c r="R6" t="n">
-        <v>143000</v>
+        <v>-86000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 조선주 급등 속 국내 증시 부진.  신용 물량 출회 및 기관 매도 우려.  하반기 산타랠리 기대감과 종목 자체의 변동성에 대한 불안감.</t>
+          <t>사상 최대 실적 발표 및 TC본더 매출 본격화로 인한 주가 상승 기대감. 과매도 구간 및 소부장 섹터 비교 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['조선주', '신용물량', '산타랠리']</t>
+          <t>['실적', 'TC본더', '과매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11340</v>
+        <v>15880</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.41%</t>
+          <t>'+1.02%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>192</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>642</v>
+        <v>169</v>
       </c>
       <c r="H7" t="n">
-        <v>9.73</v>
+        <v>28.13</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11620</v>
+        <v>15720</v>
       </c>
       <c r="K7" t="n">
-        <v>11300</v>
+        <v>15420</v>
       </c>
       <c r="L7" t="n">
-        <v>11470</v>
+        <v>16050</v>
       </c>
       <c r="M7" t="n">
-        <v>10960</v>
+        <v>15320</v>
       </c>
       <c r="N7" t="n">
-        <v>9.6</v>
+        <v>28.07</v>
       </c>
       <c r="O7" t="n">
-        <v>20373415205</v>
+        <v>18258038680</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>15320</v>
       </c>
       <c r="R7" t="n">
-        <v>64000</v>
+        <v>143000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>공매도 금지 조치 및 원전, 가덕도 공사비 증액 등 정부 정책 관련 긍정적 기대감.  한수원과의 협상 및 재입찰 관련 불확실성 존재.</t>
+          <t>미국 조선주 강세와 대비되는 국내 증시 상황. 신용 물량 출회 및 기관 매수 타이밍 관련 논의.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도금지', '원전', '가덕도']</t>
+          <t>['조선주', '신용 물량', '기관 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55300</v>
+        <v>54900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.47%</t>
+          <t>'-3.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.2</v>
       </c>
       <c r="E8" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F8" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G8" t="n">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="H8" t="n">
         <v>22.14</v>
@@ -1162,7 +1162,7 @@
         <v>22.34</v>
       </c>
       <c r="O8" t="n">
-        <v>26314008300</v>
+        <v>30582463050</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 폴란드 원전 사업 기대감.  정부 정책 및 실적 부진에 대한 비판과 시장 변동성에 대한 우려.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 호조에도 불구하고 주가 하락. 체코 원전 수주 실패 및 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['SMR', '원전', '뉴스케일']</t>
+          <t>['SMR', '뉴스케일파워', '체코 원전']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>222500</v>
+        <v>11140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-4.09%</t>
+          <t>'-4.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>210</v>
       </c>
       <c r="F9" t="n">
-        <v>539</v>
+        <v>122</v>
       </c>
       <c r="G9" t="n">
-        <v>1404</v>
+        <v>705</v>
       </c>
       <c r="H9" t="n">
-        <v>46.17</v>
+        <v>9.73</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>232000</v>
+        <v>11620</v>
       </c>
       <c r="K9" t="n">
-        <v>223500</v>
+        <v>11300</v>
       </c>
       <c r="L9" t="n">
-        <v>229500</v>
+        <v>11470</v>
       </c>
       <c r="M9" t="n">
-        <v>221000</v>
+        <v>10960</v>
       </c>
       <c r="N9" t="n">
-        <v>46.19</v>
+        <v>9.6</v>
       </c>
       <c r="O9" t="n">
-        <v>918063697000</v>
+        <v>22978444185</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>1198000</v>
+        <v>64000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재용 증여세, 노조 주가 하락 기도 등 총수 관련 부정적 이슈와 해외 상장 기대감 혼재.  주가 변동성 및 국장 시장 전반에 대한 비판.</t>
+          <t>한수원 갑질 논란 및 가덕도 공사비 증액 이슈 속 공매도 금지 조치. 러시아, 우크라이나, 중동 재건 관련 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['증여세', '노조', '레버리지']</t>
+          <t>['원전', '공매도 금지', '가덕도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14320</v>
+        <v>221750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.72%</t>
+          <t>'-4.42%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>538</v>
       </c>
       <c r="G10" t="n">
-        <v>182</v>
+        <v>1337</v>
       </c>
       <c r="H10" t="n">
-        <v>3.13</v>
+        <v>46.17</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>15030</v>
+        <v>232000</v>
       </c>
       <c r="K10" t="n">
-        <v>14500</v>
+        <v>223500</v>
       </c>
       <c r="L10" t="n">
-        <v>14570</v>
+        <v>229500</v>
       </c>
       <c r="M10" t="n">
-        <v>14010</v>
+        <v>221000</v>
       </c>
       <c r="N10" t="n">
-        <v>3.33</v>
+        <v>46.19</v>
       </c>
       <c r="O10" t="n">
-        <v>17152014460</v>
+        <v>1013813069500</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>1830</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>7000</v>
+        <v>1198000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>광통신 섹터 전반의 하락세와 개별 종목의 변동성에 대한 부정적 심리. 명확한 근거 제시 부족.</t>
+          <t>이재용 회장의 경영 행태와 상속세 문제로 인한 주가 하락 및 주주 불만 제기. 미국 증시 상장 이슈 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '변동성', '국장']</t>
+          <t>['상속세', '주가 하락', '경영 행태']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1427000</v>
+        <v>14170</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.49%</t>
+          <t>'-5.72%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.06</v>
+        <v>-0.2</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>504</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>1462</v>
+        <v>202</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72</v>
+        <v>3.13</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1526000</v>
+        <v>15030</v>
       </c>
       <c r="K11" t="n">
-        <v>1444000</v>
+        <v>14500</v>
       </c>
       <c r="L11" t="n">
-        <v>1446000</v>
+        <v>14570</v>
       </c>
       <c r="M11" t="n">
-        <v>1408000</v>
+        <v>14010</v>
       </c>
       <c r="N11" t="n">
-        <v>48.66</v>
+        <v>3.33</v>
       </c>
       <c r="O11" t="n">
-        <v>1045317384000</v>
+        <v>19955521350</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>501000</v>
+        <v>1830</v>
       </c>
       <c r="R11" t="n">
-        <v>-20000</v>
+        <v>7000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 및 외인 매도세 지속.  대규모 소각에도 주가 방어 실패, 하락 추세 강화.  향후 증시 및 개별 종목에 대한 부정적 전망.</t>
+          <t>광통신 관련 특허 및 해외 기업과의 연관성 언급. 주가 하락에 대한 우려와 데드크로스 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '외인매도', '소각']</t>
+          <t>['광통신', '특허', '데드크로스']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21900</v>
+        <v>1410000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.20%</t>
+          <t>'-7.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.63</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>118</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>96</v>
+        <v>509</v>
       </c>
       <c r="G12" t="n">
-        <v>302</v>
+        <v>1391</v>
       </c>
       <c r="H12" t="n">
-        <v>11.6</v>
+        <v>48.72</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>23600</v>
+        <v>1526000</v>
       </c>
       <c r="K12" t="n">
-        <v>22650</v>
+        <v>1444000</v>
       </c>
       <c r="L12" t="n">
-        <v>22700</v>
+        <v>1446000</v>
       </c>
       <c r="M12" t="n">
-        <v>21100</v>
+        <v>1408000</v>
       </c>
       <c r="N12" t="n">
-        <v>12.23</v>
+        <v>48.66</v>
       </c>
       <c r="O12" t="n">
-        <v>39616600225</v>
+        <v>1200316543000</v>
       </c>
       <c r="P12" t="n">
-        <v>59300</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>21100</v>
+        <v>501000</v>
       </c>
       <c r="R12" t="n">
-        <v>-368000</v>
+        <v>-20000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>한화 김동원 부회장 주가 누르기 의혹 제기.  태양광 수혜 및 RE100 승인 호재와 급락세, IR 신뢰도 부족, 주가 조작 의혹 등 부정적 요인 혼재.</t>
+          <t>반도체 업황 부진 및 외인 기관 매도세 속 주가 하락. 3분기 매출 및 자사주 소각 관련 내용 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['태양광', 'RE100', '주가조작']</t>
+          <t>['반도체', '외인 매도', '자사주 소각']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,86 +1568,86 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13890</v>
+        <v>21800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-18.29%</t>
+          <t>'-7.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.63</v>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>47</v>
+        <v>331</v>
       </c>
       <c r="H13" t="n">
-        <v>0.66</v>
+        <v>11.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17000</v>
+        <v>23600</v>
       </c>
       <c r="K13" t="n">
-        <v>14000</v>
+        <v>22650</v>
       </c>
       <c r="L13" t="n">
-        <v>14900</v>
+        <v>22700</v>
       </c>
       <c r="M13" t="n">
-        <v>13260</v>
+        <v>21100</v>
       </c>
       <c r="N13" t="n">
-        <v>0.65</v>
+        <v>12.23</v>
       </c>
       <c r="O13" t="n">
-        <v>19428918305</v>
+        <v>44443171825</v>
       </c>
       <c r="P13" t="n">
-        <v>28800</v>
+        <v>59300</v>
       </c>
       <c r="Q13" t="n">
-        <v>11550</v>
+        <v>21100</v>
       </c>
       <c r="R13" t="n">
-        <v>12000</v>
+        <v>-368000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 업황 부진과 신규주 상장 관련 부정적 전망. 보호예수 해제 이후 주가 하락 우려.</t>
+          <t>한화 김동원 부회장 주가 누르기 의혹 및 태양광 사업 실적 호조에도 불구하고 주가 급락. RE100 승인 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '신규주', '보호예수']</t>
+          <t>['주가 조작', '태양광', 'RE100']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10260</v>
+        <v>13520</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-31.60%</t>
+          <t>'-20.47%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F14" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="H14" t="n">
-        <v>3.05</v>
+        <v>0.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,58 +1699,150 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="K14" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14900</v>
+      </c>
+      <c r="M14" t="n">
+        <v>13260</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O14" t="n">
+        <v>22137040185</v>
+      </c>
+      <c r="P14" t="n">
+        <v>28800</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>11550</v>
+      </c>
+      <c r="R14" t="n">
         <v>12000</v>
       </c>
-      <c r="L14" t="n">
-        <v>12700</v>
-      </c>
-      <c r="M14" t="n">
-        <v>9800</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>43033260540</v>
-      </c>
-      <c r="P14" t="n">
-        <v>12700</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>9800</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-28000</v>
-      </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>동시 상장 종목 대비 낮은 현재가와 높은 당기순이익.  공모주 시장 전반의 부진 및 투자자들의 부정적 심리.</t>
+          <t>반도체 생산량 3배 증가 및 HBM 관련 대형 업체들과의 연관성 언급. 보호예수 물량 소화 후 주가 상승 기대감과 프로그램 매매 동향.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['HBM', '보호예수', '데이터센터']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10170</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-32.20%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>119</v>
+      </c>
+      <c r="F15" t="n">
+        <v>74</v>
+      </c>
+      <c r="G15" t="n">
+        <v>107</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>12700</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9790</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>46656923625</v>
+      </c>
+      <c r="P15" t="n">
+        <v>12700</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>9790</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-28000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>공모주 상장 후 급락세. 높은 당기순이익 대비 낮은 시가총액으로 인한 저평가 논란. 환매 관련 언급.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
         <v>0.2</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>['공모주', '당기순이익', '하한가']</t>
-        </is>
-      </c>
-      <c r="X14" t="n">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['공모주', '상장 폐지', '당기순이익']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>1</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>439270</t>
         </is>

--- a/data/trending_integrated_20261030_09.xlsx
+++ b/data/trending_integrated_20261030_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19570</v>
+        <v>18730</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+117.44%</t>
+          <t>'+108.11%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F2" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>165991256720</v>
+        <v>177124353125</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장 후 단기 급등세를 보이며 높은 수익률 기록. 유통 물량 적고 변동성 큰 특성 언급.</t>
+          <t>신규 상장주로서 높은 변동성과 단기 급등 가능성. 유통 물량 적음. 투기적 거래 경향.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규 상장', '단타', '유통 물량']</t>
+          <t>['신규주', '단타', '유통물량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12600</v>
+        <v>12790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.50%</t>
+          <t>'+14.20%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="F3" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G3" t="n">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="H3" t="n">
         <v>15.04</v>
@@ -702,7 +702,7 @@
         <v>15.08</v>
       </c>
       <c r="O3" t="n">
-        <v>22165343120</v>
+        <v>24529475935</v>
       </c>
       <c r="P3" t="n">
         <v>18960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 및 100억 달러 시장 석권 전망. 공매도 세력의 움직임과 높은 거래대금 기록.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 성공. 100억 달러 규모의 백색 LED 시장 석권 기대. 기술 개발 기반 주가 상승 및 공매도 세력과의 경쟁 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['백색LED', '희토류', '시장 석권']</t>
+          <t>['백색 LED', '희토류', '시장 석권']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>상지건설</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6680</v>
+        <v>18370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.05%</t>
+          <t>'+10.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6240</v>
+        <v>16650</v>
       </c>
       <c r="K4" t="n">
-        <v>6700</v>
+        <v>16830</v>
       </c>
       <c r="L4" t="n">
-        <v>7670</v>
+        <v>19550</v>
       </c>
       <c r="M4" t="n">
-        <v>6330</v>
+        <v>16750</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>11046430195</v>
+        <v>50325599940</v>
       </c>
       <c r="P4" t="n">
-        <v>16620</v>
+        <v>22450</v>
       </c>
       <c r="Q4" t="n">
-        <v>4600</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>건설 경기 전환점 및 풍부한 재료를 기반으로 한 주봉 차트 분석. 유상증자 이후의 불확실성 언급.</t>
+          <t>11월 양자 관련법 시행 최대 수혜주로 부각. 보안 섹터 내 기술력 및 대장주 가능성 기대. 단, 과거 개미 등치기 이력 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['건설 경기', '주봉 차트', '유상증자']</t>
+          <t>['양자', '보안', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042940</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8900</v>
+        <v>9100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.73%</t>
+          <t>'+6.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="H5" t="n">
         <v>2.67</v>
@@ -886,7 +886,7 @@
         <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>17140192560</v>
+        <v>18240243055</v>
       </c>
       <c r="P5" t="n">
         <v>19270</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>인텔 어닝 쇼크 및 환기 관련 이슈로 인한 주가 변동성. 광통신 사업 및 혁신 기술 관련 기대감.</t>
+          <t>장기 상승세 전망과 함께 광통신 기술과의 연계 가능성 제시. 다만, 기관 매수세 부진 및 외국인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '환기', '혁신']</t>
+          <t>['광통신', '장기 상승', '양산']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>상지건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50400</v>
+        <v>6600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.65%</t>
+          <t>'+5.77%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="H6" t="n">
-        <v>23.82</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>49100</v>
+        <v>6240</v>
       </c>
       <c r="K6" t="n">
-        <v>49450</v>
+        <v>6700</v>
       </c>
       <c r="L6" t="n">
-        <v>52000</v>
+        <v>7670</v>
       </c>
       <c r="M6" t="n">
-        <v>48050</v>
+        <v>6330</v>
       </c>
       <c r="N6" t="n">
-        <v>24.64</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>29769251700</v>
+        <v>11384807455</v>
       </c>
       <c r="P6" t="n">
-        <v>97900</v>
+        <v>16620</v>
       </c>
       <c r="Q6" t="n">
-        <v>30950</v>
+        <v>4600</v>
       </c>
       <c r="R6" t="n">
-        <v>-86000</v>
+        <v>25000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표 및 TC본더 매출 본격화로 인한 주가 상승 기대감. 과매도 구간 및 소부장 섹터 비교 언급.</t>
+          <t>건설 경기 전환점 및 풍부한 재료를 기반으로 한 주봉 차트 분석. 유상증자 이후의 불확실성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', '과매도']</t>
+          <t>['건설 경기', '주봉 차트', '유상증자']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>042940</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15880</v>
+        <v>15930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.02%</t>
+          <t>'+1.34%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="H7" t="n">
         <v>28.13</v>
@@ -1070,7 +1070,7 @@
         <v>28.07</v>
       </c>
       <c r="O7" t="n">
-        <v>18258038680</v>
+        <v>20193365795</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 조선주 강세와 대비되는 국내 증시 상황. 신용 물량 출회 및 기관 매수 타이밍 관련 논의.</t>
+          <t>미국 조선주 강세 속 한국 조선주 상승 기대감. 단기 급등 후 하락 가능성 및 신용 물량 부담 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['조선주', '신용 물량', '기관 매수']</t>
+          <t>['조선주', '미국', '단타']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54900</v>
+        <v>49600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.17%</t>
+          <t>'+1.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.2</v>
+        <v>-0.82</v>
       </c>
       <c r="E8" t="n">
-        <v>155</v>
+        <v>62</v>
       </c>
       <c r="F8" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>595</v>
+        <v>117</v>
       </c>
       <c r="H8" t="n">
-        <v>22.14</v>
+        <v>23.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>56700</v>
+        <v>49100</v>
       </c>
       <c r="K8" t="n">
-        <v>55500</v>
+        <v>49450</v>
       </c>
       <c r="L8" t="n">
-        <v>55900</v>
+        <v>52000</v>
       </c>
       <c r="M8" t="n">
-        <v>54000</v>
+        <v>48050</v>
       </c>
       <c r="N8" t="n">
-        <v>22.34</v>
+        <v>24.64</v>
       </c>
       <c r="O8" t="n">
-        <v>30582463050</v>
+        <v>31688536550</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>97900</v>
       </c>
       <c r="Q8" t="n">
-        <v>53400</v>
+        <v>30950</v>
       </c>
       <c r="R8" t="n">
-        <v>19000</v>
+        <v>-86000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 호조에도 불구하고 주가 하락. 체코 원전 수주 실패 및 정부 정책 비판.</t>
+          <t>사상 최대 실적 발표와 TC본더 매출 본격화로 인한 실적 개선 기대감. 낮은 PER 대비 높은 기술력 및 글로벌 수요 증가.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['SMR', '뉴스케일파워', '체코 원전']</t>
+          <t>['실적', 'TC본더', '수요']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11140</v>
+        <v>54900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-4.13%</t>
+          <t>'-3.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="F9" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G9" t="n">
-        <v>705</v>
+        <v>612</v>
       </c>
       <c r="H9" t="n">
-        <v>9.73</v>
+        <v>22.14</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11620</v>
+        <v>56700</v>
       </c>
       <c r="K9" t="n">
-        <v>11300</v>
+        <v>55500</v>
       </c>
       <c r="L9" t="n">
-        <v>11470</v>
+        <v>55900</v>
       </c>
       <c r="M9" t="n">
-        <v>10960</v>
+        <v>54000</v>
       </c>
       <c r="N9" t="n">
-        <v>9.6</v>
+        <v>22.34</v>
       </c>
       <c r="O9" t="n">
-        <v>22978444185</v>
+        <v>32839514500</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>53400</v>
       </c>
       <c r="R9" t="n">
-        <v>64000</v>
+        <v>19000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>한수원 갑질 논란 및 가덕도 공사비 증액 이슈 속 공매도 금지 조치. 러시아, 우크라이나, 중동 재건 관련 기대감.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선. 다만, 체코 원전 사업 실패 경험과 정치적 불확실성으로 인한 변동성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '공매도 금지', '가덕도']</t>
+          <t>['SMR', '뉴스케일파워', '원전']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>221750</v>
+        <v>11170</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.42%</t>
+          <t>'-3.87%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>217</v>
       </c>
       <c r="F10" t="n">
-        <v>538</v>
+        <v>125</v>
       </c>
       <c r="G10" t="n">
-        <v>1337</v>
+        <v>730</v>
       </c>
       <c r="H10" t="n">
-        <v>46.17</v>
+        <v>9.73</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>232000</v>
+        <v>11620</v>
       </c>
       <c r="K10" t="n">
-        <v>223500</v>
+        <v>11300</v>
       </c>
       <c r="L10" t="n">
-        <v>229500</v>
+        <v>11470</v>
       </c>
       <c r="M10" t="n">
-        <v>221000</v>
+        <v>10960</v>
       </c>
       <c r="N10" t="n">
-        <v>46.19</v>
+        <v>9.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1013813069500</v>
+        <v>24226399950</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>1198000</v>
+        <v>64000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이재용 회장의 경영 행태와 상속세 문제로 인한 주가 하락 및 주주 불만 제기. 미국 증시 상장 이슈 언급.</t>
+          <t>한수원 갑질 논란 속 가덕도 신공항 사업 증액과 공매도 금지 조치가 호재로 작용할 가능성. 원전 사업 참여 여부 불확실.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['상속세', '주가 하락', '경영 행태']</t>
+          <t>['가덕도', '공매도', '원전']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14170</v>
+        <v>221750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.72%</t>
+          <t>'-4.42%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>542</v>
       </c>
       <c r="G11" t="n">
-        <v>202</v>
+        <v>1232</v>
       </c>
       <c r="H11" t="n">
-        <v>3.13</v>
+        <v>46.17</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15030</v>
+        <v>232000</v>
       </c>
       <c r="K11" t="n">
-        <v>14500</v>
+        <v>223500</v>
       </c>
       <c r="L11" t="n">
-        <v>14570</v>
+        <v>229500</v>
       </c>
       <c r="M11" t="n">
-        <v>14010</v>
+        <v>221000</v>
       </c>
       <c r="N11" t="n">
-        <v>3.33</v>
+        <v>46.19</v>
       </c>
       <c r="O11" t="n">
-        <v>19955521350</v>
+        <v>1063945476750</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1830</v>
+        <v>94500</v>
       </c>
       <c r="R11" t="n">
-        <v>7000</v>
+        <v>1198000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>광통신 관련 특허 및 해외 기업과의 연관성 언급. 주가 하락에 대한 우려와 데드크로스 가능성 언급.</t>
+          <t>이재용 회장의 상속세 및 증여세 관련 논란과 노조 문제로 인한 주가 하락 우려. 외인 배당 기대감은 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '특허', '데드크로스']</t>
+          <t>['이재용', '증여세', '배당']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1410000</v>
+        <v>14220</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.60%</t>
+          <t>'-5.39%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>-0.2</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
-        <v>509</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>1391</v>
+        <v>208</v>
       </c>
       <c r="H12" t="n">
-        <v>48.72</v>
+        <v>3.13</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1526000</v>
+        <v>15030</v>
       </c>
       <c r="K12" t="n">
-        <v>1444000</v>
+        <v>14500</v>
       </c>
       <c r="L12" t="n">
-        <v>1446000</v>
+        <v>14570</v>
       </c>
       <c r="M12" t="n">
-        <v>1408000</v>
+        <v>14010</v>
       </c>
       <c r="N12" t="n">
-        <v>48.66</v>
+        <v>3.33</v>
       </c>
       <c r="O12" t="n">
-        <v>1200316543000</v>
+        <v>20859701485</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>501000</v>
+        <v>1830</v>
       </c>
       <c r="R12" t="n">
-        <v>-20000</v>
+        <v>7000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 및 외인 기관 매도세 속 주가 하락. 3분기 매출 및 자사주 소각 관련 내용 언급.</t>
+          <t>광통신 관련 특허 및 해외 기업과의 연관성 언급. 주가 하락에 대한 우려와 데드크로스 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '외인 매도', '자사주 소각']</t>
+          <t>['광통신', '특허', '데드크로스']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21800</v>
+        <v>21850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-7.63%</t>
+          <t>'-7.42%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.63</v>
       </c>
       <c r="E13" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G13" t="n">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="H13" t="n">
         <v>11.6</v>
@@ -1622,7 +1622,7 @@
         <v>12.23</v>
       </c>
       <c r="O13" t="n">
-        <v>44443171825</v>
+        <v>46558501775</v>
       </c>
       <c r="P13" t="n">
         <v>59300</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>한화 김동원 부회장 주가 누르기 의혹 및 태양광 사업 실적 호조에도 불구하고 주가 급락. RE100 승인 언급.</t>
+          <t>태양광 사업 호조에도 불구하고 주가 급락세 지속. 김동원 부회장 주가 누르기 의혹 제기. IR 신뢰도 부족.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 조작', '태양광', 'RE100']</t>
+          <t>['태양광', '주가누르기', 'IR']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13520</v>
+        <v>1412000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-20.47%</t>
+          <t>'-7.47%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>84</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>502</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>1323</v>
       </c>
       <c r="H14" t="n">
-        <v>0.66</v>
+        <v>48.72</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17000</v>
+        <v>1526000</v>
       </c>
       <c r="K14" t="n">
-        <v>14000</v>
+        <v>1444000</v>
       </c>
       <c r="L14" t="n">
-        <v>14900</v>
+        <v>1446000</v>
       </c>
       <c r="M14" t="n">
-        <v>13260</v>
+        <v>1408000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.65</v>
+        <v>48.66</v>
       </c>
       <c r="O14" t="n">
-        <v>22137040185</v>
+        <v>1285292099500</v>
       </c>
       <c r="P14" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>11550</v>
+        <v>501000</v>
       </c>
       <c r="R14" t="n">
-        <v>12000</v>
+        <v>-20000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 생산량 3배 증가 및 HBM 관련 대형 업체들과의 연관성 언급. 보호예수 물량 소화 후 주가 상승 기대감과 프로그램 매매 동향.</t>
+          <t>반도체 섹터 전반의 급락세와 외국인 매도세 지속. 주가 방어 실패 및 계단식 하락 우려. 대규모 소각 효과 미미.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['HBM', '보호예수', '데이터센터']</t>
+          <t>['반도체', '외인', '하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10170</v>
+        <v>13690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-32.20%</t>
+          <t>'-19.47%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="H15" t="n">
-        <v>3.05</v>
+        <v>0.66</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,58 +1791,150 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="K15" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14900</v>
+      </c>
+      <c r="M15" t="n">
+        <v>13260</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O15" t="n">
+        <v>23014635875</v>
+      </c>
+      <c r="P15" t="n">
+        <v>28800</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>11550</v>
+      </c>
+      <c r="R15" t="n">
         <v>12000</v>
       </c>
-      <c r="L15" t="n">
-        <v>12700</v>
-      </c>
-      <c r="M15" t="n">
-        <v>9790</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>46656923625</v>
-      </c>
-      <c r="P15" t="n">
-        <v>12700</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>9790</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-28000</v>
-      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공모주 상장 후 급락세. 높은 당기순이익 대비 낮은 시가총액으로 인한 저평가 논란. 환매 관련 언급.</t>
+          <t>보호예수 물량 해소 후 저가 매수 기회 포착. HBM 및 데이터센터 관련 성장 기대감 속 국내 유일 마이크론 ASML 퀠테스트 통과 기업으로 분석.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공모주', '상장 폐지', '당기순이익']</t>
+          <t>['보호예수', 'HBM', '퀠테스트']</t>
         </is>
       </c>
       <c r="X15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10720</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-28.53%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>142</v>
+      </c>
+      <c r="F16" t="n">
+        <v>80</v>
+      </c>
+      <c r="G16" t="n">
+        <v>137</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12700</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9790</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>56099152180</v>
+      </c>
+      <c r="P16" t="n">
+        <v>12700</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>9790</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-28000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>높은 당기순이익과 현금 보유량으로 인한 알짜배기 기업 평가. 동시 상장한 인텔리빅스와의 비교 우위. 다만, 높은 변동성과 하따 위험 존재.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['당기순이익', '알짜배기', '하따']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
         <v>1</v>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>439270</t>
         </is>
